--- a/artfynd/A 16513-2022 artfynd.xlsx
+++ b/artfynd/A 16513-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16513-2022 artfynd.xlsx
+++ b/artfynd/A 16513-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104023368</v>
+        <v>104023372</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1841</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544597.2356585627</v>
+        <v>544236</v>
       </c>
       <c r="R2" t="n">
-        <v>7093422.878909602</v>
+        <v>7093304</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -799,16 +789,11 @@
         <v>104023374</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544167.7278872636</v>
+        <v>544168</v>
       </c>
       <c r="R3" t="n">
-        <v>7093459.397520246</v>
+        <v>7093460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -915,12 +900,7 @@
         <v>104023373</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544026.991543278</v>
+        <v>544027</v>
       </c>
       <c r="R4" t="n">
-        <v>7093361.61624085</v>
+        <v>7093362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,12 +1016,7 @@
         <v>104023375</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544234.735348935</v>
+        <v>544235</v>
       </c>
       <c r="R5" t="n">
-        <v>7093450.239515929</v>
+        <v>7093450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,6 +1122,122 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104023368</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544597</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7093423</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 16513-2022 artfynd.xlsx
+++ b/artfynd/A 16513-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023372</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023368</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,8 +1267,20 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023375</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>